--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DFS_HRM-2031-0112/panel_11/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DFS_HRM-2031-0112/panel_11/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.50486</v>
+        <v>17.07101</v>
       </c>
       <c r="D2" t="n">
         <v>16.25751</v>
       </c>
       <c r="E2" t="n">
-        <v>17.07101</v>
+        <v>16.50486</v>
       </c>
       <c r="F2" t="n">
         <v>41.4624</v>
@@ -488,10 +488,10 @@
         <v>16.62183</v>
       </c>
       <c r="D3" t="n">
+        <v>16.29212</v>
+      </c>
+      <c r="E3" t="n">
         <v>16.46461</v>
-      </c>
-      <c r="E3" t="n">
-        <v>16.29212</v>
       </c>
       <c r="F3" t="n">
         <v>42.02538</v>
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.3875</v>
+        <v>16.56315</v>
       </c>
       <c r="D4" t="n">
         <v>16.35492</v>
       </c>
       <c r="E4" t="n">
-        <v>16.56315</v>
+        <v>16.3875</v>
       </c>
       <c r="F4" t="n">
         <v>42.6861</v>
@@ -535,13 +535,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.66057</v>
+        <v>16.71604</v>
       </c>
       <c r="D5" t="n">
         <v>16.46772</v>
       </c>
       <c r="E5" t="n">
-        <v>16.71604</v>
+        <v>16.66057</v>
       </c>
       <c r="F5" t="n">
         <v>41.97284</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.57507</v>
+        <v>17.24248</v>
       </c>
       <c r="D7" t="n">
         <v>16.43608</v>
       </c>
       <c r="E7" t="n">
-        <v>17.24248</v>
+        <v>16.57507</v>
       </c>
       <c r="F7" t="n">
         <v>41.91593</v>
@@ -613,10 +613,10 @@
         <v>16.91772</v>
       </c>
       <c r="D8" t="n">
+        <v>16.55761</v>
+      </c>
+      <c r="E8" t="n">
         <v>16.66243</v>
-      </c>
-      <c r="E8" t="n">
-        <v>16.55761</v>
       </c>
       <c r="F8" t="n">
         <v>42.27112</v>
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.45702</v>
+        <v>16.55493</v>
       </c>
       <c r="D9" t="n">
         <v>16.12004</v>
       </c>
       <c r="E9" t="n">
-        <v>16.55493</v>
+        <v>16.45702</v>
       </c>
       <c r="F9" t="n">
         <v>41.89789</v>
